--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-26).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-26).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R$ 9.551,54</t>
-  </si>
-  <si>
-    <t>97.8</t>
-  </si>
-  <si>
-    <t>61.7</t>
-  </si>
-  <si>
-    <t>6.78</t>
-  </si>
-  <si>
-    <t>20.9</t>
-  </si>
-  <si>
-    <t>7.3</t>
-  </si>
-  <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>34.5%</t>
-  </si>
-  <si>
-    <t>16.3%</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 9.545,83</t>
+  </si>
+  <si>
+    <t>97.3</t>
+  </si>
+  <si>
+    <t>61.6</t>
+  </si>
+  <si>
+    <t>6.82</t>
+  </si>
+  <si>
+    <t>21.2</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>33.9%</t>
+  </si>
+  <si>
+    <t>16.2%</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -980,25 +980,25 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>5.8%</t>
+    <t>5.7%</t>
   </si>
   <si>
     <t>4.9%</t>
   </si>
   <si>
-    <t>2084.0</t>
-  </si>
-  <si>
-    <t>1769.0</t>
-  </si>
-  <si>
-    <t>146.0</t>
-  </si>
-  <si>
-    <t>62.0</t>
-  </si>
-  <si>
-    <t>293.0</t>
+    <t>2107.0</t>
+  </si>
+  <si>
+    <t>1791.0</t>
+  </si>
+  <si>
+    <t>149.0</t>
+  </si>
+  <si>
+    <t>63.0</t>
+  </si>
+  <si>
+    <t>296.0</t>
   </si>
   <si>
     <t>102.0</t>
@@ -1007,16 +1007,16 @@
     <t>29.0</t>
   </si>
   <si>
-    <t>625.0</t>
-  </si>
-  <si>
-    <t>295.0</t>
-  </si>
-  <si>
-    <t>531.0</t>
-  </si>
-  <si>
-    <t>63.0</t>
+    <t>627.0</t>
+  </si>
+  <si>
+    <t>297.0</t>
+  </si>
+  <si>
+    <t>543.0</t>
+  </si>
+  <si>
+    <t>64.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3272,7 +3272,9 @@
       <c r="N13" s="6">
         <v>135</v>
       </c>
-      <c r="O13" s="6"/>
+      <c r="O13" s="6">
+        <v>89</v>
+      </c>
       <c r="P13" s="7">
         <v>8.5050127819548873</v>
       </c>
@@ -3282,31 +3284,75 @@
       <c r="R13" s="8">
         <v>10.398863636363636</v>
       </c>
-      <c r="S13" s="8"/>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
       <c r="T13" s="9">
         <v>0.06741573033707865</v>
       </c>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="U13" s="9">
+        <v>0.1797752808988764</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0.02247191011235955</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.011235955056179775</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0.011235955056179775</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.011235955056179775</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.11235955056179775</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>10</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0.011235955056179775</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -4909,7 +4955,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4939,14 +4985,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>11175.92</v>
+      </c>
+      <c r="N24" s="6">
+        <v>125</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>7.7436636363636362</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>25.497569791666667</v>
+      </c>
+      <c r="R24" s="8">
+        <v>10.771701041666667</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.041666666666666664</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -9254,7 +9312,9 @@
       <c r="N53" s="6">
         <v>76</v>
       </c>
-      <c r="O53" s="6"/>
+      <c r="O53" s="6">
+        <v>44</v>
+      </c>
       <c r="P53" s="7">
         <v>3.5037276315789474</v>
       </c>
@@ -9264,31 +9324,75 @@
       <c r="R53" s="8">
         <v>4.6651522727272727</v>
       </c>
-      <c r="S53" s="8"/>
+      <c r="S53" s="8">
+        <v>7</v>
+      </c>
       <c r="T53" s="9">
         <v>0.63636363636363635</v>
       </c>
-      <c r="U53" s="9"/>
-      <c r="V53" s="9"/>
-      <c r="W53" s="9"/>
-      <c r="X53" s="9"/>
-      <c r="Y53" s="9"/>
-      <c r="Z53" s="9"/>
-      <c r="AA53" s="9"/>
-      <c r="AB53" s="9"/>
-      <c r="AC53" s="9"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AF53" s="6"/>
-      <c r="AG53" s="6"/>
-      <c r="AH53" s="6"/>
-      <c r="AI53" s="6"/>
-      <c r="AJ53" s="6"/>
-      <c r="AK53" s="6"/>
-      <c r="AL53" s="6"/>
-      <c r="AM53" s="6"/>
-      <c r="AN53" s="9"/>
-      <c r="AO53" s="6"/>
+      <c r="U53" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="V53" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="W53" s="9">
+        <v>0</v>
+      </c>
+      <c r="X53" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="Y53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AD53" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF53" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP53" s="4">
         <v>58</v>
       </c>
@@ -10016,7 +10120,7 @@
         <v>0.030612244897959183</v>
       </c>
       <c r="W58" s="9">
-        <v>0</v>
+        <v>0.010204081631999999</v>
       </c>
       <c r="X58" s="9">
         <v>0.01020408163265306</v>
@@ -10046,7 +10150,7 @@
         <v>3</v>
       </c>
       <c r="AG58" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH58" s="6">
         <v>1</v>
@@ -10736,7 +10840,7 @@
         <v>19632</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>51</v>
@@ -10766,8 +10870,12 @@
         <v>58</v>
       </c>
       <c r="L63" s="4"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="6"/>
+      <c r="M63" s="5">
+        <v>0</v>
+      </c>
+      <c r="N63" s="6">
+        <v>0</v>
+      </c>
       <c r="O63" s="6"/>
       <c r="P63" s="7"/>
       <c r="Q63" s="8"/>
@@ -12589,7 +12697,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12617,35 +12725,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>11076.360000000001</v>
+      </c>
+      <c r="N76" s="6">
+        <v>123</v>
+      </c>
+      <c r="O76" s="6">
+        <v>72</v>
+      </c>
+      <c r="P76" s="7">
+        <v>6.5527559055118116</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>41.696065277777777</v>
+      </c>
+      <c r="R76" s="8">
+        <v>26.282176388888889</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -14504,7 +14670,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14532,14 +14698,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>11174.9</v>
+      </c>
+      <c r="N89" s="6">
+        <v>102</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>13.918300980392157</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>34.191176470588232</v>
+      </c>
+      <c r="R89" s="8">
+        <v>11.387907843137256</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -31946,7 +32124,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>51</v>
@@ -31976,35 +32154,93 @@
         <v>58</v>
       </c>
       <c r="L207" s="4"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="6"/>
-      <c r="O207" s="6"/>
-      <c r="P207" s="7"/>
-      <c r="Q207" s="8"/>
-      <c r="R207" s="8"/>
-      <c r="S207" s="8"/>
-      <c r="T207" s="9"/>
-      <c r="U207" s="9"/>
-      <c r="V207" s="9"/>
-      <c r="W207" s="9"/>
-      <c r="X207" s="9"/>
-      <c r="Y207" s="9"/>
-      <c r="Z207" s="9"/>
-      <c r="AA207" s="9"/>
-      <c r="AB207" s="9"/>
-      <c r="AC207" s="9"/>
-      <c r="AD207" s="6"/>
-      <c r="AE207" s="6"/>
-      <c r="AF207" s="6"/>
-      <c r="AG207" s="6"/>
-      <c r="AH207" s="6"/>
-      <c r="AI207" s="6"/>
-      <c r="AJ207" s="6"/>
-      <c r="AK207" s="6"/>
-      <c r="AL207" s="6"/>
-      <c r="AM207" s="6"/>
-      <c r="AN207" s="9"/>
-      <c r="AO207" s="6"/>
+      <c r="M207" s="5">
+        <v>3740.5900000000001</v>
+      </c>
+      <c r="N207" s="6">
+        <v>40</v>
+      </c>
+      <c r="O207" s="6">
+        <v>19</v>
+      </c>
+      <c r="P207" s="7">
+        <v>7.4258763157894734</v>
+      </c>
+      <c r="Q207" s="8">
+        <v>21.077194736842106</v>
+      </c>
+      <c r="R207" s="8">
+        <v>7.4447368421052627</v>
+      </c>
+      <c r="S207" s="8">
+        <v>7</v>
+      </c>
+      <c r="T207" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="U207" s="9">
+        <v>0</v>
+      </c>
+      <c r="V207" s="9">
+        <v>0</v>
+      </c>
+      <c r="W207" s="9">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP207" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-26).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-26).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>29</t>
+    <t>23</t>
   </si>
   <si>
-    <t>R$ 9.545,83</t>
+    <t>R$ 9.479,90</t>
   </si>
   <si>
-    <t>97.3</t>
+    <t>96.6</t>
   </si>
   <si>
-    <t>61.6</t>
+    <t>61.3</t>
   </si>
   <si>
     <t>6.82</t>
   </si>
   <si>
-    <t>21.2</t>
+    <t>21.1</t>
   </si>
   <si>
-    <t>7.4</t>
+    <t>7.3</t>
   </si>
   <si>
-    <t>6.1</t>
+    <t>6.3</t>
   </si>
   <si>
-    <t>33.9%</t>
+    <t>33.7%</t>
   </si>
   <si>
-    <t>16.2%</t>
+    <t>15.9%</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -971,7 +971,7 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>2.7%</t>
+    <t>2.6%</t>
   </si>
   <si>
     <t>0.9%</t>
@@ -980,43 +980,37 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>5.7%</t>
+    <t>5.6%</t>
   </si>
   <si>
-    <t>4.9%</t>
+    <t>4.8%</t>
   </si>
   <si>
-    <t>2107.0</t>
+    <t>2144.0</t>
   </si>
   <si>
-    <t>1791.0</t>
+    <t>1824.0</t>
   </si>
   <si>
-    <t>149.0</t>
-  </si>
-  <si>
-    <t>63.0</t>
-  </si>
-  <si>
-    <t>296.0</t>
-  </si>
-  <si>
-    <t>102.0</t>
-  </si>
-  <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>627.0</t>
-  </si>
-  <si>
-    <t>297.0</t>
-  </si>
-  <si>
-    <t>543.0</t>
+    <t>150.0</t>
   </si>
   <si>
     <t>64.0</t>
+  </si>
+  <si>
+    <t>303.0</t>
+  </si>
+  <si>
+    <t>103.0</t>
+  </si>
+  <si>
+    <t>30.0</t>
+  </si>
+  <si>
+    <t>639.0</t>
+  </si>
+  <si>
+    <t>552.0</t>
   </si>
   <si>
     <t>1</t>
@@ -2203,7 +2197,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2233,35 +2227,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>13346</v>
+      </c>
+      <c r="N6" s="6">
+        <v>127</v>
+      </c>
+      <c r="O6" s="6">
+        <v>95</v>
+      </c>
+      <c r="P6" s="7">
+        <v>5.5958992063492063</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>14.835263157894737</v>
+      </c>
+      <c r="R6" s="8">
+        <v>2.083864893617021</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.56842105263157894</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.084210526315789472</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0.010526315789473684</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.031578947368421054</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.031578947368421054</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0.021052631578947368</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -6791,7 +6843,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6821,35 +6873,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>6984.4200000000001</v>
+      </c>
+      <c r="N36" s="6">
+        <v>69</v>
+      </c>
+      <c r="O36" s="6">
+        <v>56</v>
+      </c>
+      <c r="P36" s="7">
+        <v>6.7862749999999998</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>19.074405357142858</v>
+      </c>
+      <c r="R36" s="8">
+        <v>5.1720232142857148</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.053571428571428568</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0.017857142857142856</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7094,7 +7204,7 @@
         <v>4.215476190476191</v>
       </c>
       <c r="S38" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" s="9">
         <v>0.51111111111111107</v>
@@ -7673,7 +7783,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7703,35 +7813,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>8615.9500000000007</v>
+      </c>
+      <c r="N42" s="6">
+        <v>89</v>
+      </c>
+      <c r="O42" s="6">
+        <v>54</v>
+      </c>
+      <c r="P42" s="7">
+        <v>5.5558939024390241</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>20.147484905660377</v>
+      </c>
+      <c r="R42" s="8">
+        <v>7.325961538461538</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.20754716981132076</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0.018518518518518517</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.018518518518518517</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0.018518518518518517</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -9022,7 +9190,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9052,35 +9220,93 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="6"/>
+      <c r="M51" s="5">
+        <v>1098.1500000000001</v>
+      </c>
+      <c r="N51" s="6">
+        <v>11</v>
+      </c>
+      <c r="O51" s="6">
+        <v>4</v>
+      </c>
+      <c r="P51" s="7">
+        <v>3.8287909090909094</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>11.279175</v>
+      </c>
+      <c r="R51" s="8">
+        <v>0.55835000000000001</v>
+      </c>
+      <c r="S51" s="8">
+        <v>7</v>
+      </c>
+      <c r="T51" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="U51" s="9">
+        <v>1</v>
+      </c>
+      <c r="V51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AB51" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AC51" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM51" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP51" s="4">
         <v>58</v>
       </c>
@@ -16595,7 +16821,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16625,35 +16851,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>7308.1899999999996</v>
+      </c>
+      <c r="N102" s="6">
+        <v>81</v>
+      </c>
+      <c r="O102" s="6">
+        <v>53</v>
+      </c>
+      <c r="P102" s="7">
+        <v>11.627642682926828</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>24.5261</v>
+      </c>
+      <c r="R102" s="8">
+        <v>6.859524489795918</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.13207547169811321</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.16981132075471697</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.037735849056603772</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.094339622641509441</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.056603773584905662</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -24785,7 +25069,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -24815,35 +25099,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>7526.7200000000003</v>
+      </c>
+      <c r="N158" s="6">
+        <v>74</v>
+      </c>
+      <c r="O158" s="6">
+        <v>51</v>
+      </c>
+      <c r="P158" s="7">
+        <v>6.6539999999999999</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>18.620260784313725</v>
+      </c>
+      <c r="R158" s="8">
+        <v>5.1411764705882348</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.13725490196078433</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0.019607843137000001</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -30438,7 +30780,9 @@
       <c r="N195" s="6">
         <v>97</v>
       </c>
-      <c r="O195" s="6"/>
+      <c r="O195" s="6">
+        <v>64</v>
+      </c>
       <c r="P195" s="7">
         <v>6.2962966666666667</v>
       </c>
@@ -30448,31 +30792,75 @@
       <c r="R195" s="8">
         <v>7.2145828124999998</v>
       </c>
-      <c r="S195" s="8"/>
+      <c r="S195" s="8">
+        <v>7</v>
+      </c>
       <c r="T195" s="9">
         <v>0.3125</v>
       </c>
-      <c r="U195" s="9"/>
-      <c r="V195" s="9"/>
-      <c r="W195" s="9"/>
-      <c r="X195" s="9"/>
-      <c r="Y195" s="9"/>
-      <c r="Z195" s="9"/>
-      <c r="AA195" s="9"/>
-      <c r="AB195" s="9"/>
-      <c r="AC195" s="9"/>
-      <c r="AD195" s="6"/>
-      <c r="AE195" s="6"/>
-      <c r="AF195" s="6"/>
-      <c r="AG195" s="6"/>
-      <c r="AH195" s="6"/>
-      <c r="AI195" s="6"/>
-      <c r="AJ195" s="6"/>
-      <c r="AK195" s="6"/>
-      <c r="AL195" s="6"/>
-      <c r="AM195" s="6"/>
-      <c r="AN195" s="9"/>
-      <c r="AO195" s="6"/>
+      <c r="U195" s="9">
+        <v>0.078125</v>
+      </c>
+      <c r="V195" s="9">
+        <v>0</v>
+      </c>
+      <c r="W195" s="9">
+        <v>0</v>
+      </c>
+      <c r="X195" s="9">
+        <v>0.046875</v>
+      </c>
+      <c r="Y195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC195" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AD195" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH195" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM195" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO195" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP195" s="4">
         <v>58</v>
       </c>
@@ -33275,16 +33663,16 @@
         <v>332</v>
       </c>
       <c t="s" r="AL216" s="11">
+        <v>329</v>
+      </c>
+      <c t="s" r="AM216" s="11">
         <v>333</v>
-      </c>
-      <c t="s" r="AM216" s="11">
-        <v>334</v>
       </c>
       <c t="s" r="AN216" s="11">
         <v>319</v>
       </c>
       <c t="s" r="AO216" s="11">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="AP216" s="12"/>
       <c t="s" r="AQ216" s="12">
@@ -33301,10 +33689,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX216" s="11">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c t="s" r="AY216" s="11">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AZ216" s="12"/>
       <c r="BA216" s="12"/>
